--- a/data/net_contest.xlsx
+++ b/data/net_contest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-90" yWindow="0" windowWidth="12780" windowHeight="16170" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="net1" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -54,6 +54,14 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -81,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -89,6 +97,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -455,7 +464,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -863,7 +872,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -1270,14 +1279,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="6"/>
+    <col width="12" customWidth="1" min="5" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1308,6 +1317,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>得分</t>
         </is>
       </c>
@@ -1323,6 +1337,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>109</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65.68000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1335,6 +1364,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>782</v>
+      </c>
+      <c r="E3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29.05</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1347,6 +1391,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>591</v>
+      </c>
+      <c r="E4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G4" t="n">
+        <v>38.77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1359,6 +1418,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>55</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G5" t="n">
+        <v>74.95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1371,6 +1445,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>305</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G6" t="n">
+        <v>52.66</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1383,6 +1472,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>591</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G7" t="n">
+        <v>38.77</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1395,6 +1499,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>301</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G8" t="n">
+        <v>52.78</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1407,6 +1526,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>630</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G9" t="n">
+        <v>43.17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1419,6 +1553,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>225</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G10" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1431,6 +1580,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1535</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8.369999999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1443,6 +1607,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1316</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14.46</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1455,6 +1634,21 @@
           <t>北京邮电大学</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>139</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G13" t="n">
+        <v>64.7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1466,6 +1660,20 @@
         <is>
           <t>北京邮电大学</t>
         </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>未参加</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/net_contest.xlsx
+++ b/data/net_contest.xlsx
@@ -1395,7 +1395,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>591</v>
+        <v>410</v>
       </c>
       <c r="E4" t="n">
         <v>13</v>
@@ -1404,7 +1404,7 @@
         <v>2107</v>
       </c>
       <c r="G4" t="n">
-        <v>38.77</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="5">
@@ -1530,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>630</v>
+        <v>201</v>
       </c>
       <c r="E9" t="n">
         <v>13</v>
@@ -1539,7 +1539,7 @@
         <v>2107</v>
       </c>
       <c r="G9" t="n">
-        <v>43.17</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="10">
